--- a/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/StructureDefinition-mii-ex-studie-backport-definitionReference.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/StructureDefinition-mii-ex-studie-backport-definitionReference.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T20:57:51+00:00</t>
+    <t>2026-08-31T21:27:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/StructureDefinition-mii-ex-studie-backport-definitionReference.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/StructureDefinition-mii-ex-studie-backport-definitionReference.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T21:27:57+00:00</t>
+    <t>2026-08-31T22:12:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/StructureDefinition-mii-ex-studie-backport-definitionReference.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/StructureDefinition-mii-ex-studie-backport-definitionReference.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T22:12:16+00:00</t>
+    <t>2026-08-31T22:17:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/StructureDefinition-mii-ex-studie-backport-definitionReference.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/StructureDefinition-mii-ex-studie-backport-definitionReference.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T22:17:14+00:00</t>
+    <t>2026-09-01T10:01:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
